--- a/history-2026-03-31.xlsx
+++ b/history-2026-03-31.xlsx
@@ -397,17 +397,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:O6"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
     <col min="3" max="3" width="9.83203125" customWidth="1"/>
-    <col min="4" max="4" width="18.83203125" customWidth="1"/>
-    <col min="5" max="5" width="18.83203125" customWidth="1"/>
-    <col min="6" max="6" width="9.83203125" customWidth="1"/>
-    <col min="7" max="7" width="8.83203125" customWidth="1"/>
-    <col min="8" max="8" width="14.83203125" customWidth="1"/>
-    <col min="9" max="9" width="19.83203125" customWidth="1"/>
+    <col min="4" max="4" width="13.83203125" customWidth="1"/>
+    <col min="5" max="5" width="23.83203125" customWidth="1"/>
+    <col min="6" max="6" width="8.83203125" customWidth="1"/>
+    <col min="7" max="7" width="10.83203125" customWidth="1"/>
+    <col min="8" max="8" width="12.83203125" customWidth="1"/>
+    <col min="9" max="9" width="11.83203125" customWidth="1"/>
+    <col min="10" max="10" width="23.83203125" customWidth="1"/>
+    <col min="11" max="11" width="23.83203125" customWidth="1"/>
+    <col min="12" max="12" width="9.83203125" customWidth="1"/>
+    <col min="13" max="13" width="8.83203125" customWidth="1"/>
+    <col min="14" max="14" width="23.83203125" customWidth="1"/>
+    <col min="15" max="15" width="132.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -421,21 +427,39 @@
         <v>scan-by</v>
       </c>
       <c r="D1" t="str">
+        <v>Part Code</v>
+      </c>
+      <c r="E1" t="str">
+        <v>LG Barcode</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Nation</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Supplier</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Mfg Date</v>
+      </c>
+      <c r="I1" t="str">
+        <v>LG Serial</v>
+      </c>
+      <c r="J1" t="str">
         <v>Generated code 1</v>
       </c>
-      <c r="E1" t="str">
+      <c r="K1" t="str">
         <v>Generated code 2</v>
       </c>
-      <c r="F1" t="str">
+      <c r="L1" t="str">
         <v>Scanner</v>
       </c>
-      <c r="G1" t="str">
+      <c r="M1" t="str">
         <v>Status</v>
       </c>
-      <c r="H1" t="str">
+      <c r="N1" t="str">
         <v>Scanned Code</v>
       </c>
-      <c r="I1" t="str">
+      <c r="O1" t="str">
         <v>Barcode Breakdown</v>
       </c>
     </row>
@@ -444,28 +468,46 @@
         <v>31/03/2026</v>
       </c>
       <c r="B2" t="str">
-        <v>10:13:33</v>
+        <v>12:13:00</v>
       </c>
       <c r="C2" t="str">
         <v/>
       </c>
       <c r="D2" t="str">
-        <v/>
+        <v>EAD63827619</v>
       </c>
       <c r="E2" t="str">
-        <v/>
+        <v>EAD63827619IGA63P0011</v>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>India</v>
       </c>
       <c r="G2" t="str">
+        <v>GA</v>
+      </c>
+      <c r="H2" t="str">
+        <v>2026/03/25</v>
+      </c>
+      <c r="I2" t="str">
+        <v>0011</v>
+      </c>
+      <c r="J2" t="str">
+        <v>EAD63827619IGA63P0011</v>
+      </c>
+      <c r="K2" t="str">
+        <v>EAD63827619IGA63P0011</v>
+      </c>
+      <c r="L2" t="str">
+        <v/>
+      </c>
+      <c r="M2" t="str">
         <v>PASS</v>
       </c>
-      <c r="H2" t="str">
-        <v/>
-      </c>
-      <c r="I2" t="str">
-        <v/>
+      <c r="N2" t="str">
+        <v>EAD63827619IGA63P0011</v>
+      </c>
+      <c r="O2" t="str">
+        <v>Part Code: EAD63827619 | LG Barcode: EAD63827619IGA63P0011 | Nation: India | Supplier: GA | Mfg Date: 2026/03/25 | LG Serial: 0011</v>
       </c>
     </row>
     <row r="3">
@@ -473,33 +515,138 @@
         <v>31/03/2026</v>
       </c>
       <c r="B3" t="str">
+        <v>12:06:43</v>
+      </c>
+      <c r="C3" t="str">
+        <v/>
+      </c>
+      <c r="D3" t="str">
+        <v>EAD63827619</v>
+      </c>
+      <c r="E3" t="str">
+        <v>EAD63827619IGA63P0009</v>
+      </c>
+      <c r="F3" t="str">
+        <v>India</v>
+      </c>
+      <c r="G3" t="str">
+        <v>GA</v>
+      </c>
+      <c r="H3" t="str">
+        <v>2026/03/25</v>
+      </c>
+      <c r="I3" t="str">
+        <v>0009</v>
+      </c>
+      <c r="J3" t="str">
+        <v>EAD63827619IGA63P0009</v>
+      </c>
+      <c r="K3" t="str">
+        <v>EAD63827619IGA63P0009</v>
+      </c>
+      <c r="L3" t="str">
+        <v/>
+      </c>
+      <c r="M3" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="N3" t="str">
+        <v>EAD63827619IGA63P0009</v>
+      </c>
+      <c r="O3" t="str">
+        <v>Part Code: EAD63827619 | LG Barcode: EAD63827619IGA63P0009 | Nation: India | Supplier: GA | Mfg Date: 2026/03/25 | LG Serial: 0009</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>31/03/2026</v>
+      </c>
+      <c r="B4" t="str">
+        <v>11:02:45</v>
+      </c>
+      <c r="C4" t="str">
+        <v/>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v/>
+      </c>
+      <c r="M4" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="N4" t="str">
+        <v/>
+      </c>
+      <c r="O4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>31/03/2026</v>
+      </c>
+      <c r="B5" t="str">
+        <v>10:13:33</v>
+      </c>
+      <c r="C5" t="str">
+        <v/>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v/>
+      </c>
+      <c r="M5" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="N5" t="str">
+        <v/>
+      </c>
+      <c r="O5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>31/03/2026</v>
+      </c>
+      <c r="B6" t="str">
         <v>08:34:58</v>
       </c>
-      <c r="C3" t="str">
-        <v/>
-      </c>
-      <c r="D3" t="str">
-        <v/>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
+      <c r="C6" t="str">
+        <v/>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v/>
+      </c>
+      <c r="M6" t="str">
         <v>PASS</v>
       </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
+      <c r="N6" t="str">
+        <v/>
+      </c>
+      <c r="O6" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O6"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/history-2026-03-31.xlsx
+++ b/history-2026-03-31.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:O7"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -409,11 +409,9 @@
     <col min="8" max="8" width="12.83203125" customWidth="1"/>
     <col min="9" max="9" width="11.83203125" customWidth="1"/>
     <col min="10" max="10" width="23.83203125" customWidth="1"/>
-    <col min="11" max="11" width="23.83203125" customWidth="1"/>
-    <col min="12" max="12" width="9.83203125" customWidth="1"/>
-    <col min="13" max="13" width="8.83203125" customWidth="1"/>
-    <col min="14" max="14" width="23.83203125" customWidth="1"/>
-    <col min="15" max="15" width="132.83203125" customWidth="1"/>
+    <col min="11" max="11" width="9.83203125" customWidth="1"/>
+    <col min="12" max="12" width="8.83203125" customWidth="1"/>
+    <col min="13" max="13" width="132.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -445,22 +443,22 @@
         <v>LG Serial</v>
       </c>
       <c r="J1" t="str">
+        <v>Scanned Code</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Scanner</v>
+      </c>
+      <c r="L1" t="str">
+        <v>Status</v>
+      </c>
+      <c r="M1" t="str">
+        <v>Barcode Breakdown</v>
+      </c>
+      <c r="N1" t="str">
         <v>Generated code 1</v>
       </c>
-      <c r="K1" t="str">
+      <c r="O1" t="str">
         <v>Generated code 2</v>
-      </c>
-      <c r="L1" t="str">
-        <v>Scanner</v>
-      </c>
-      <c r="M1" t="str">
-        <v>Status</v>
-      </c>
-      <c r="N1" t="str">
-        <v>Scanned Code</v>
-      </c>
-      <c r="O1" t="str">
-        <v>Barcode Breakdown</v>
       </c>
     </row>
     <row r="2">
@@ -468,7 +466,7 @@
         <v>31/03/2026</v>
       </c>
       <c r="B2" t="str">
-        <v>12:13:00</v>
+        <v>12:16:10</v>
       </c>
       <c r="C2" t="str">
         <v/>
@@ -477,7 +475,7 @@
         <v>EAD63827619</v>
       </c>
       <c r="E2" t="str">
-        <v>EAD63827619IGA63P0011</v>
+        <v>EAD63827619IGA63P0012</v>
       </c>
       <c r="F2" t="str">
         <v>India</v>
@@ -489,25 +487,19 @@
         <v>2026/03/25</v>
       </c>
       <c r="I2" t="str">
-        <v>0011</v>
+        <v>0012</v>
       </c>
       <c r="J2" t="str">
-        <v>EAD63827619IGA63P0011</v>
+        <v>EAD63827619IGA63P0012</v>
       </c>
       <c r="K2" t="str">
-        <v>EAD63827619IGA63P0011</v>
+        <v/>
       </c>
       <c r="L2" t="str">
-        <v/>
+        <v>PASS</v>
       </c>
       <c r="M2" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="N2" t="str">
-        <v>EAD63827619IGA63P0011</v>
-      </c>
-      <c r="O2" t="str">
-        <v>Part Code: EAD63827619 | LG Barcode: EAD63827619IGA63P0011 | Nation: India | Supplier: GA | Mfg Date: 2026/03/25 | LG Serial: 0011</v>
+        <v>Part Code: EAD63827619 | LG Barcode: EAD63827619IGA63P0012 | Nation: India | Supplier: GA | Mfg Date: 2026/03/25 | LG Serial: 0012</v>
       </c>
     </row>
     <row r="3">
@@ -515,7 +507,7 @@
         <v>31/03/2026</v>
       </c>
       <c r="B3" t="str">
-        <v>12:06:43</v>
+        <v>12:13:00</v>
       </c>
       <c r="C3" t="str">
         <v/>
@@ -524,7 +516,7 @@
         <v>EAD63827619</v>
       </c>
       <c r="E3" t="str">
-        <v>EAD63827619IGA63P0009</v>
+        <v>EAD63827619IGA63P0011</v>
       </c>
       <c r="F3" t="str">
         <v>India</v>
@@ -536,25 +528,25 @@
         <v>2026/03/25</v>
       </c>
       <c r="I3" t="str">
-        <v>0009</v>
+        <v>0011</v>
       </c>
       <c r="J3" t="str">
-        <v>EAD63827619IGA63P0009</v>
+        <v>EAD63827619IGA63P0011</v>
       </c>
       <c r="K3" t="str">
-        <v>EAD63827619IGA63P0009</v>
+        <v/>
       </c>
       <c r="L3" t="str">
-        <v/>
+        <v>PASS</v>
       </c>
       <c r="M3" t="str">
-        <v>PASS</v>
+        <v>Part Code: EAD63827619 | LG Barcode: EAD63827619IGA63P0011 | Nation: India | Supplier: GA | Mfg Date: 2026/03/25 | LG Serial: 0011</v>
       </c>
       <c r="N3" t="str">
-        <v>EAD63827619IGA63P0009</v>
+        <v>EAD63827619IGA63P0011</v>
       </c>
       <c r="O3" t="str">
-        <v>Part Code: EAD63827619 | LG Barcode: EAD63827619IGA63P0009 | Nation: India | Supplier: GA | Mfg Date: 2026/03/25 | LG Serial: 0009</v>
+        <v>EAD63827619IGA63P0011</v>
       </c>
     </row>
     <row r="4">
@@ -562,28 +554,46 @@
         <v>31/03/2026</v>
       </c>
       <c r="B4" t="str">
-        <v>11:02:45</v>
+        <v>12:06:43</v>
       </c>
       <c r="C4" t="str">
         <v/>
       </c>
+      <c r="D4" t="str">
+        <v>EAD63827619</v>
+      </c>
+      <c r="E4" t="str">
+        <v>EAD63827619IGA63P0009</v>
+      </c>
+      <c r="F4" t="str">
+        <v>India</v>
+      </c>
+      <c r="G4" t="str">
+        <v>GA</v>
+      </c>
+      <c r="H4" t="str">
+        <v>2026/03/25</v>
+      </c>
+      <c r="I4" t="str">
+        <v>0009</v>
+      </c>
       <c r="J4" t="str">
-        <v/>
+        <v>EAD63827619IGA63P0009</v>
       </c>
       <c r="K4" t="str">
         <v/>
       </c>
       <c r="L4" t="str">
-        <v/>
+        <v>PASS</v>
       </c>
       <c r="M4" t="str">
-        <v>PASS</v>
+        <v>Part Code: EAD63827619 | LG Barcode: EAD63827619IGA63P0009 | Nation: India | Supplier: GA | Mfg Date: 2026/03/25 | LG Serial: 0009</v>
       </c>
       <c r="N4" t="str">
-        <v/>
+        <v>EAD63827619IGA63P0009</v>
       </c>
       <c r="O4" t="str">
-        <v/>
+        <v>EAD63827619IGA63P0009</v>
       </c>
     </row>
     <row r="5">
@@ -591,7 +601,7 @@
         <v>31/03/2026</v>
       </c>
       <c r="B5" t="str">
-        <v>10:13:33</v>
+        <v>11:02:45</v>
       </c>
       <c r="C5" t="str">
         <v/>
@@ -603,10 +613,10 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v/>
+        <v>PASS</v>
       </c>
       <c r="M5" t="str">
-        <v>PASS</v>
+        <v/>
       </c>
       <c r="N5" t="str">
         <v/>
@@ -620,33 +630,62 @@
         <v>31/03/2026</v>
       </c>
       <c r="B6" t="str">
+        <v>10:13:33</v>
+      </c>
+      <c r="C6" t="str">
+        <v/>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M6" t="str">
+        <v/>
+      </c>
+      <c r="N6" t="str">
+        <v/>
+      </c>
+      <c r="O6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>31/03/2026</v>
+      </c>
+      <c r="B7" t="str">
         <v>08:34:58</v>
       </c>
-      <c r="C6" t="str">
-        <v/>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v/>
-      </c>
-      <c r="M6" t="str">
+      <c r="C7" t="str">
+        <v/>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
         <v>PASS</v>
       </c>
-      <c r="N6" t="str">
-        <v/>
-      </c>
-      <c r="O6" t="str">
+      <c r="M7" t="str">
+        <v/>
+      </c>
+      <c r="N7" t="str">
+        <v/>
+      </c>
+      <c r="O7" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O7"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/history-2026-03-31.xlsx
+++ b/history-2026-03-31.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:O8"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -466,7 +466,7 @@
         <v>31/03/2026</v>
       </c>
       <c r="B2" t="str">
-        <v>12:16:10</v>
+        <v>12:17:55</v>
       </c>
       <c r="C2" t="str">
         <v/>
@@ -496,10 +496,10 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="M2" t="str">
-        <v>Part Code: EAD63827619 | LG Barcode: EAD63827619IGA63P0012 | Nation: India | Supplier: GA | Mfg Date: 2026/03/25 | LG Serial: 0012</v>
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -507,7 +507,7 @@
         <v>31/03/2026</v>
       </c>
       <c r="B3" t="str">
-        <v>12:13:00</v>
+        <v>12:16:10</v>
       </c>
       <c r="C3" t="str">
         <v/>
@@ -516,7 +516,7 @@
         <v>EAD63827619</v>
       </c>
       <c r="E3" t="str">
-        <v>EAD63827619IGA63P0011</v>
+        <v>EAD63827619IGA63P0012</v>
       </c>
       <c r="F3" t="str">
         <v>India</v>
@@ -528,10 +528,10 @@
         <v>2026/03/25</v>
       </c>
       <c r="I3" t="str">
-        <v>0011</v>
+        <v>0012</v>
       </c>
       <c r="J3" t="str">
-        <v>EAD63827619IGA63P0011</v>
+        <v>EAD63827619IGA63P0012</v>
       </c>
       <c r="K3" t="str">
         <v/>
@@ -540,13 +540,7 @@
         <v>PASS</v>
       </c>
       <c r="M3" t="str">
-        <v>Part Code: EAD63827619 | LG Barcode: EAD63827619IGA63P0011 | Nation: India | Supplier: GA | Mfg Date: 2026/03/25 | LG Serial: 0011</v>
-      </c>
-      <c r="N3" t="str">
-        <v>EAD63827619IGA63P0011</v>
-      </c>
-      <c r="O3" t="str">
-        <v>EAD63827619IGA63P0011</v>
+        <v>Part Code: EAD63827619 | LG Barcode: EAD63827619IGA63P0012 | Nation: India | Supplier: GA | Mfg Date: 2026/03/25 | LG Serial: 0012</v>
       </c>
     </row>
     <row r="4">
@@ -554,7 +548,7 @@
         <v>31/03/2026</v>
       </c>
       <c r="B4" t="str">
-        <v>12:06:43</v>
+        <v>12:13:00</v>
       </c>
       <c r="C4" t="str">
         <v/>
@@ -563,7 +557,7 @@
         <v>EAD63827619</v>
       </c>
       <c r="E4" t="str">
-        <v>EAD63827619IGA63P0009</v>
+        <v>EAD63827619IGA63P0011</v>
       </c>
       <c r="F4" t="str">
         <v>India</v>
@@ -575,10 +569,10 @@
         <v>2026/03/25</v>
       </c>
       <c r="I4" t="str">
-        <v>0009</v>
+        <v>0011</v>
       </c>
       <c r="J4" t="str">
-        <v>EAD63827619IGA63P0009</v>
+        <v>EAD63827619IGA63P0011</v>
       </c>
       <c r="K4" t="str">
         <v/>
@@ -587,13 +581,13 @@
         <v>PASS</v>
       </c>
       <c r="M4" t="str">
-        <v>Part Code: EAD63827619 | LG Barcode: EAD63827619IGA63P0009 | Nation: India | Supplier: GA | Mfg Date: 2026/03/25 | LG Serial: 0009</v>
+        <v>Part Code: EAD63827619 | LG Barcode: EAD63827619IGA63P0011 | Nation: India | Supplier: GA | Mfg Date: 2026/03/25 | LG Serial: 0011</v>
       </c>
       <c r="N4" t="str">
-        <v>EAD63827619IGA63P0009</v>
+        <v>EAD63827619IGA63P0011</v>
       </c>
       <c r="O4" t="str">
-        <v>EAD63827619IGA63P0009</v>
+        <v>EAD63827619IGA63P0011</v>
       </c>
     </row>
     <row r="5">
@@ -601,13 +595,31 @@
         <v>31/03/2026</v>
       </c>
       <c r="B5" t="str">
-        <v>11:02:45</v>
+        <v>12:06:43</v>
       </c>
       <c r="C5" t="str">
         <v/>
       </c>
+      <c r="D5" t="str">
+        <v>EAD63827619</v>
+      </c>
+      <c r="E5" t="str">
+        <v>EAD63827619IGA63P0009</v>
+      </c>
+      <c r="F5" t="str">
+        <v>India</v>
+      </c>
+      <c r="G5" t="str">
+        <v>GA</v>
+      </c>
+      <c r="H5" t="str">
+        <v>2026/03/25</v>
+      </c>
+      <c r="I5" t="str">
+        <v>0009</v>
+      </c>
       <c r="J5" t="str">
-        <v/>
+        <v>EAD63827619IGA63P0009</v>
       </c>
       <c r="K5" t="str">
         <v/>
@@ -616,13 +628,13 @@
         <v>PASS</v>
       </c>
       <c r="M5" t="str">
-        <v/>
+        <v>Part Code: EAD63827619 | LG Barcode: EAD63827619IGA63P0009 | Nation: India | Supplier: GA | Mfg Date: 2026/03/25 | LG Serial: 0009</v>
       </c>
       <c r="N5" t="str">
-        <v/>
+        <v>EAD63827619IGA63P0009</v>
       </c>
       <c r="O5" t="str">
-        <v/>
+        <v>EAD63827619IGA63P0009</v>
       </c>
     </row>
     <row r="6">
@@ -630,7 +642,7 @@
         <v>31/03/2026</v>
       </c>
       <c r="B6" t="str">
-        <v>10:13:33</v>
+        <v>11:02:45</v>
       </c>
       <c r="C6" t="str">
         <v/>
@@ -659,7 +671,7 @@
         <v>31/03/2026</v>
       </c>
       <c r="B7" t="str">
-        <v>08:34:58</v>
+        <v>10:13:33</v>
       </c>
       <c r="C7" t="str">
         <v/>
@@ -680,12 +692,41 @@
         <v/>
       </c>
       <c r="O7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>31/03/2026</v>
+      </c>
+      <c r="B8" t="str">
+        <v>08:34:58</v>
+      </c>
+      <c r="C8" t="str">
+        <v/>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="M8" t="str">
+        <v/>
+      </c>
+      <c r="N8" t="str">
+        <v/>
+      </c>
+      <c r="O8" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O8"/>
   </ignoredErrors>
 </worksheet>
 </file>